--- a/daily_logs/daily_2026-05-27.xlsx
+++ b/daily_logs/daily_2026-05-27.xlsx
@@ -18,9 +18,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -236,7 +235,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -275,7 +274,8 @@
     <xf numFmtId="58" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -674,7 +674,7 @@
           <t>Date</t>
         </is>
       </c>
-      <c r="B4" s="30" t="n">
+      <c r="B4" s="31" t="n">
         <v>46169</v>
       </c>
       <c r="C4" s="28" t="n"/>
@@ -2916,6 +2916,10 @@
         <is>
           <t>HY OAS 20dd=10.0bp [OK]
 HY OAS 5dd=9.0bp
+HYG 5d=0.8% [OK]
+HYG DD%=None% max drawdown
+FXY 5d=-0.3% [OK]
+SPY vs 200MA: above ($SPY=750.5900268554688, 200MA=676.9)
 Extreme: VIX&gt;35•HYOAS&gt;5%•SOFR-IORB&gt;+5bp</t>
         </is>
       </c>

--- a/daily_logs/daily_2026-05-27.xlsx
+++ b/daily_logs/daily_2026-05-27.xlsx
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="E11" s="24" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F11" s="24" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="E12" s="24" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
@@ -880,10 +880,10 @@
         </is>
       </c>
       <c r="E13" s="24" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="E15" s="24" t="n">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="F15" s="24" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G15" s="6" t="n"/>
     </row>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="E16" s="24" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F16" s="24" t="n">
         <v>10</v>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="E18" s="24" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="F18" s="24" t="n">
-        <v>-27</v>
+        <v>-19</v>
       </c>
       <c r="G18" s="6" t="n"/>
     </row>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="E19" s="24" t="n">
-        <v>4.56</v>
+        <v>4.5</v>
       </c>
       <c r="F19" s="24" t="n">
-        <v>-25</v>
+        <v>-15</v>
       </c>
       <c r="G19" s="6" t="n"/>
     </row>
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="E20" s="24" t="n">
-        <v>5.07</v>
+        <v>5.03</v>
       </c>
       <c r="F20" s="24" t="n">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="G20" s="6" t="n"/>
     </row>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="E29" s="24" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="F29" s="24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G29" s="6" t="n"/>
     </row>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="E32" s="24" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="F32" s="24" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="E38" s="24" t="n">
-        <v>-10</v>
+        <v>-2</v>
       </c>
       <c r="F38" s="24" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="E40" s="24" t="n">
-        <v>-7</v>
+        <v>1</v>
       </c>
       <c r="F40" s="24" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G40" s="6" t="n"/>
     </row>
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="E43" s="24" t="n">
-        <v>3.55</v>
+        <v>3.63</v>
       </c>
       <c r="F43" s="24" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G43" s="6" t="n"/>
     </row>
@@ -2010,10 +2010,10 @@
         </is>
       </c>
       <c r="E51" s="24" t="n">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F51" s="24" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
@@ -2221,10 +2221,10 @@
         </is>
       </c>
       <c r="E58" s="24" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F58" s="24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
@@ -2914,8 +2914,8 @@
       <c r="E91" s="29" t="n"/>
       <c r="F91" s="21" t="inlineStr">
         <is>
-          <t>HY OAS 20dd=10.0bp [OK]
-HY OAS 5dd=9.0bp
+          <t>HY OAS 20dd=13.0bp [OK]
+HY OAS 5dd=14.0bp
 HYG 5d=0.8% [OK]
 HYG DD%=None% max drawdown
 FXY 5d=-0.3% [OK]
